--- a/task177/golden/retention_offer_forecast_2027.xlsx
+++ b/task177/golden/retention_offer_forecast_2027.xlsx
@@ -106,7 +106,7 @@
     <t>Family</t>
   </si>
   <si>
-    <t>Half-price discounts on the bills of subscriptions that took last January's offer, in the email, on the web or in the app, by the month the bill was raised; pounds to the nearest hundred. The save desk's own half price is not the offer.</t>
+    <t>Half-price discounts on the bills of subscriptions that took last January's offer, in the email, on the web or in the app, by the month the bill was raised; pounds to the nearest hundred. App acceptances the offers engine did not apply were billed at the app's half-price rate with no discount line, and are counted. The save desk's own half price is not the offer.</t>
   </si>
   <si>
     <t>October 2026 (GBP)</t>
@@ -121,7 +121,7 @@
     <t>January 2027 (GBP)</t>
   </si>
   <si>
-    <t>What the subscriptions on this year's list were billed for their plans, after credits, by the UK date each bill was raised; pounds to the nearest hundred. Each subscription's own invoice lines, on whichever account's invoice they sit; the Puzzles add-ons and other plans on the same invoices are not the list's plans.</t>
+    <t>What the subscriptions on this year's list were billed for their plans, net of credit notes and the goodwill credits on its invoices, by the UK date each bill was raised; pounds to the nearest hundred. Each subscription's own invoice lines, on whichever account's invoice they sit, a line billing two subscriptions of a household counted once; the Puzzles add-ons and other plans on the same invoices are not the list's plans.</t>
   </si>
   <si>
     <t>As of</t>

--- a/task177/golden/retention_offer_forecast_2027.xlsx
+++ b/task177/golden/retention_offer_forecast_2027.xlsx
@@ -106,7 +106,7 @@
     <t>Family</t>
   </si>
   <si>
-    <t>Half-price discounts on the bills of subscriptions that took last January's offer, in the email, on the web or in the app, by the month the bill was raised; pounds to the nearest hundred. App acceptances the offers engine did not apply were billed at the app's half-price rate with no discount line, and are counted. The save desk's own half price is not the offer.</t>
+    <t>Half-price discounts on the bills of subscriptions that took last January's offer, in the email, on the web or in the app, by the month the bill was raised; pounds to the nearest hundred. Discount lines and the credits posted against an acceptance once a bill had been raised are both the offer; app acceptances the offers engine did not apply were billed at the app's half-price rate with no discount line, and are counted. The save desk's own half price is not the offer.</t>
   </si>
   <si>
     <t>October 2026 (GBP)</t>
@@ -121,7 +121,7 @@
     <t>January 2027 (GBP)</t>
   </si>
   <si>
-    <t>What the subscriptions on this year's list were billed for their plans, net of credit notes and the goodwill credits on its invoices, by the UK date each bill was raised; pounds to the nearest hundred. Each subscription's own invoice lines, on whichever account's invoice they sit, a line billing two subscriptions of a household counted once; the Puzzles add-ons and other plans on the same invoices are not the list's plans.</t>
+    <t>What the subscriptions on this year's list were billed for their plans, net of credit notes and the goodwill credits on its invoices, by the UK date each bill was raised; pounds to the nearest hundred. Each subscription's own invoice lines, on whichever account's invoice they sit, one unit of each (a line of qty 2 also bills the household's other subscription); the Puzzles add-ons and other plans on the same invoices are not the list's plans.</t>
   </si>
   <si>
     <t>As of</t>
